--- a/experiment_results/combined_sweep/rtt_bursts_S1_atk10pct_wu500000.xlsx
+++ b/experiment_results/combined_sweep/rtt_bursts_S1_atk10pct_wu500000.xlsx
@@ -476,22 +476,22 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>00:009.7</t>
+          <t>00:010.0</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>18.1</t>
+          <t>16.8</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>20.0</t>
+          <t>19.4</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>1.27</t>
+          <t>1.20</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -516,7 +516,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>68</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -533,27 +533,27 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>00:020.4</t>
+          <t>00:020.0</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>34.1</t>
+          <t>24.2</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>55.5</t>
+          <t>35.7</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1.58</t>
+          <t>1.60</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>0.31</t>
+          <t>0.40</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -563,7 +563,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>17.93</t>
+          <t>10.69</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -573,7 +573,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>11426</t>
+          <t>2100</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -583,34 +583,34 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>DDoS Burst</t>
+          <t>Normal/Residual</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>00:030.1</t>
+          <t>00:030.0</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>38.3</t>
+          <t>30.4</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>56.4</t>
+          <t>42.0</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>1.72</t>
+          <t>1.86</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0.14</t>
+          <t>0.25</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -620,7 +620,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>6.16</t>
+          <t>5.59</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -630,7 +630,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>22494</t>
+          <t>5464</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -647,27 +647,27 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>00:040.0</t>
+          <t>00:040.2</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>31.8</t>
+          <t>34.5</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>40.1</t>
+          <t>44.0</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>1.93</t>
+          <t>1.82</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>0.21</t>
+          <t>0.04</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -677,17 +677,17 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>3.13</t>
+          <t>5.09</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>26558</t>
+          <t>12805</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -697,34 +697,34 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>Normal/Residual</t>
+          <t>DDoS Burst</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>00:050.1</t>
+          <t>00:050.0</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>30.6</t>
+          <t>35.0</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>38.4</t>
+          <t>44.3</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>1.64</t>
+          <t>1.84</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>0.30</t>
+          <t>0.02</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -734,7 +734,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>5.29</t>
+          <t>4.76</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -744,7 +744,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>29382</t>
+          <t>20756</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -754,7 +754,7 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>Normal/Residual</t>
+          <t>DDoS Burst</t>
         </is>
       </c>
     </row>
@@ -766,22 +766,22 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>26.8</t>
+          <t>30.9</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>33.5</t>
+          <t>40.0</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.45</t>
+          <t>1.77</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>0.19</t>
+          <t>0.06</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -791,7 +791,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>5.55</t>
+          <t>4.45</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -801,7 +801,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>27964</t>
+          <t>24727</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -811,34 +811,34 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>Normal/Residual</t>
+          <t>DDoS Burst</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>01:009.9</t>
+          <t>01:010.0</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>35.0</t>
+          <t>30.4</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>47.7</t>
+          <t>39.6</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>1.62</t>
+          <t>1.75</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>0.17</t>
+          <t>0.03</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -848,7 +848,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>10.32</t>
+          <t>4.11</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -858,7 +858,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>35432</t>
+          <t>28204</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -875,27 +875,27 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>01:020.1</t>
+          <t>01:019.7</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>41.9</t>
+          <t>32.9</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>54.8</t>
+          <t>51.2</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>1.83</t>
+          <t>1.55</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0.20</t>
+          <t>0.19</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -905,7 +905,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>7.08</t>
+          <t>9.44</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -915,7 +915,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>50273</t>
+          <t>33780</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -932,27 +932,27 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>01:029.8</t>
+          <t>01:029.9</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>36.1</t>
+          <t>32.0</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>47.1</t>
+          <t>50.4</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>1.78</t>
+          <t>1.52</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>0.05</t>
+          <t>0.04</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -962,7 +962,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>4.71</t>
+          <t>7.25</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -972,7 +972,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>58868</t>
+          <t>38385</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -989,27 +989,27 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>01:040.0</t>
+          <t>01:040.4</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>32.3</t>
+          <t>29.9</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>44.5</t>
+          <t>42.6</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>1.62</t>
+          <t>1.56</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>0.16</t>
+          <t>0.04</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -1019,7 +1019,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>5.48</t>
+          <t>5.67</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1029,7 +1029,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>63247</t>
+          <t>41303</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1046,27 +1046,27 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>01:049.9</t>
+          <t>01:050.3</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>32.1</t>
+          <t>29.0</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>44.1</t>
+          <t>42.2</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>1.59</t>
+          <t>1.51</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>0.05</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -1076,7 +1076,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>5.89</t>
+          <t>6.76</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1086,7 +1086,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>67450</t>
+          <t>43577</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1103,27 +1103,27 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>02:000.1</t>
+          <t>02:000.2</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>33.6</t>
+          <t>26.5</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>43.0</t>
+          <t>36.2</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>1.71</t>
+          <t>1.48</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>0.12</t>
+          <t>0.03</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -1133,7 +1133,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>5.25</t>
+          <t>5.26</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1143,7 +1143,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>73535</t>
+          <t>43549</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -1153,34 +1153,34 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>DDoS Burst</t>
+          <t>Normal/Residual</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>02:009.7</t>
+          <t>02:009.9</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>51.4</t>
+          <t>37.1</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>76.2</t>
+          <t>61.0</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>1.34</t>
+          <t>0.95</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>0.37</t>
+          <t>0.53</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -1190,7 +1190,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>10.65</t>
+          <t>12.75</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1200,7 +1200,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>99503</t>
+          <t>53307</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -1217,27 +1217,27 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>02:019.9</t>
+          <t>02:020.3</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>52.1</t>
+          <t>40.2</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>77.4</t>
+          <t>61.3</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>1.36</t>
+          <t>1.07</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>0.13</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -1247,7 +1247,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>5.77</t>
+          <t>7.38</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1257,7 +1257,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>125610</t>
+          <t>66072</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -1274,27 +1274,27 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>02:030.1</t>
+          <t>02:030.0</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>39.9</t>
+          <t>33.3</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>54.3</t>
+          <t>39.5</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>1.73</t>
+          <t>1.97</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>0.37</t>
+          <t>0.90</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -1304,17 +1304,17 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>4.49</t>
+          <t>3.00</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Sim</t>
+          <t>Não</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>138650</t>
+          <t>72574</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -1331,27 +1331,27 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>02:039.7</t>
+          <t>02:039.6</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>31.1</t>
+          <t>24.8</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>47.4</t>
+          <t>32.7</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>1.48</t>
+          <t>1.64</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>0.25</t>
+          <t>0.34</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1361,7 +1361,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>6.63</t>
+          <t>4.83</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -1371,7 +1371,7 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>141837</t>
+          <t>71030</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -1388,27 +1388,27 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>02:050.1</t>
+          <t>02:049.5</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>18.7</t>
+          <t>15.7</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>20.9</t>
+          <t>18.8</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>1.30</t>
+          <t>1.13</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>0.18</t>
+          <t>0.51</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>2.46</t>
+          <t>0.85</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -1428,7 +1428,7 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>132601</t>
+          <t>62525</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -1445,27 +1445,27 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>02:055.3</t>
+          <t>02:055.1</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>18.5</t>
+          <t>16.5</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>20.2</t>
+          <t>19.3</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>1.35</t>
+          <t>1.14</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>0.05</t>
+          <t>0.02</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1475,7 +1475,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>2.22</t>
+          <t>1.96</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -1485,7 +1485,7 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>127931</t>
+          <t>58921</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">

--- a/experiment_results/combined_sweep/rtt_bursts_S1_atk10pct_wu500000.xlsx
+++ b/experiment_results/combined_sweep/rtt_bursts_S1_atk10pct_wu500000.xlsx
@@ -481,17 +481,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>16.8</t>
+          <t>20.1</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>19.4</t>
+          <t>36.7</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>1.20</t>
+          <t>0.96</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -516,12 +516,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>68</t>
+          <t>2619</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -533,27 +533,27 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>00:020.0</t>
+          <t>00:020.4</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>24.2</t>
+          <t>118.8</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>35.7</t>
+          <t>229.9</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1.60</t>
+          <t>1.30</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>0.40</t>
+          <t>0.34</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -563,7 +563,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>10.69</t>
+          <t>33.23</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -573,7 +573,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>2100</t>
+          <t>76054</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -583,34 +583,34 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>Normal/Residual</t>
+          <t>DDoS Burst</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>00:030.0</t>
+          <t>00:030.1</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>30.4</t>
+          <t>138.8</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>42.0</t>
+          <t>225.5</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>1.86</t>
+          <t>1.59</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0.25</t>
+          <t>0.30</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -620,7 +620,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>5.59</t>
+          <t>4.88</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -630,7 +630,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>5464</t>
+          <t>164241</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -647,27 +647,27 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>00:040.2</t>
+          <t>00:040.1</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>34.5</t>
+          <t>70.7</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>44.0</t>
+          <t>98.6</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>1.82</t>
+          <t>1.48</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>0.04</t>
+          <t>0.11</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -677,17 +677,17 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>5.09</t>
+          <t>2.42</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Sim</t>
+          <t>Não</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>12805</t>
+          <t>192500</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -704,27 +704,27 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>00:050.0</t>
+          <t>00:049.8</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>35.0</t>
+          <t>52.3</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>44.3</t>
+          <t>77.5</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>1.84</t>
+          <t>1.66</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>0.17</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -734,7 +734,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>4.76</t>
+          <t>3.92</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -744,7 +744,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>20756</t>
+          <t>204138</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -761,27 +761,27 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>00:060.0</t>
+          <t>01:000.2</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>30.9</t>
+          <t>35.9</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>52.7</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.77</t>
+          <t>1.73</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>0.06</t>
+          <t>0.07</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -791,17 +791,17 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>4.45</t>
+          <t>3.14</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Sim</t>
+          <t>Não</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>24727</t>
+          <t>201960</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -811,34 +811,34 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>DDoS Burst</t>
+          <t>Normal/Residual</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>01:010.0</t>
+          <t>01:009.7</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>30.4</t>
+          <t>35.5</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>39.6</t>
+          <t>53.7</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>1.75</t>
+          <t>1.67</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>0.06</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -848,7 +848,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>4.11</t>
+          <t>5.57</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -858,7 +858,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>28204</t>
+          <t>199439</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -868,34 +868,34 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>DDoS Burst</t>
+          <t>Normal/Residual</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>01:019.7</t>
+          <t>01:020.1</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>32.9</t>
+          <t>34.4</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>51.2</t>
+          <t>49.0</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>1.67</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0.19</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -905,7 +905,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>9.44</t>
+          <t>5.47</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -915,7 +915,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>33780</t>
+          <t>195927</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -925,34 +925,34 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>DDoS Burst</t>
+          <t>Normal/Residual</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>01:029.9</t>
+          <t>01:030.1</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>32.0</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>50.4</t>
+          <t>151.6</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>1.52</t>
+          <t>1.50</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>0.04</t>
+          <t>0.16</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -962,7 +962,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>7.25</t>
+          <t>18.00</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -972,7 +972,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>38385</t>
+          <t>250910</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -989,27 +989,27 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>01:040.4</t>
+          <t>01:040.2</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>29.9</t>
+          <t>140.0</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>42.6</t>
+          <t>182.7</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>1.56</t>
+          <t>1.95</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>0.04</t>
+          <t>0.45</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -1019,7 +1019,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>5.67</t>
+          <t>5.39</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1029,7 +1029,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>41303</t>
+          <t>341398</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1039,29 +1039,29 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>Normal/Residual</t>
+          <t>DDoS Burst</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>01:050.3</t>
+          <t>01:050.0</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>29.0</t>
+          <t>135.5</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>42.2</t>
+          <t>185.0</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>1.51</t>
+          <t>2.00</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -1076,7 +1076,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>6.76</t>
+          <t>3.96</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1086,7 +1086,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>43577</t>
+          <t>431360</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1096,34 +1096,34 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>Normal/Residual</t>
+          <t>DDoS Burst</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>02:000.2</t>
+          <t>01:059.9</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>26.5</t>
+          <t>108.4</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>36.2</t>
+          <t>157.3</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>1.48</t>
+          <t>1.83</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>0.17</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -1133,17 +1133,17 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>5.26</t>
+          <t>3.43</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Sim</t>
+          <t>Não</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>43549</t>
+          <t>497317</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -1153,34 +1153,34 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>Normal/Residual</t>
+          <t>DDoS Burst</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>02:009.9</t>
+          <t>02:010.1</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>37.1</t>
+          <t>61.3</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>61.0</t>
+          <t>95.2</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>0.95</t>
+          <t>1.14</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>0.53</t>
+          <t>0.69</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -1190,7 +1190,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>12.75</t>
+          <t>4.47</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1200,7 +1200,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>53307</t>
+          <t>519239</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -1217,27 +1217,27 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>02:020.3</t>
+          <t>02:019.9</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>40.2</t>
+          <t>61.3</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>61.3</t>
+          <t>97.0</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>1.07</t>
+          <t>1.12</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>0.13</t>
+          <t>0.02</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -1247,7 +1247,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>7.38</t>
+          <t>7.87</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1257,7 +1257,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>66072</t>
+          <t>541198</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -1274,27 +1274,27 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>02:030.0</t>
+          <t>02:029.9</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>33.3</t>
+          <t>57.3</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>39.5</t>
+          <t>87.7</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>1.97</t>
+          <t>1.39</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>0.90</t>
+          <t>0.27</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -1304,17 +1304,17 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>3.00</t>
+          <t>4.56</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>72574</t>
+          <t>558822</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -1336,22 +1336,22 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>24.8</t>
+          <t>37.9</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>32.7</t>
+          <t>67.6</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>1.64</t>
+          <t>0.87</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>0.34</t>
+          <t>0.52</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1361,7 +1361,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>4.83</t>
+          <t>5.08</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -1371,7 +1371,7 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>71030</t>
+          <t>558405</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -1381,34 +1381,34 @@
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>Normal/Residual</t>
+          <t>DDoS Burst</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>02:049.5</t>
+          <t>02:049.9</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>15.7</t>
+          <t>17.9</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>18.8</t>
+          <t>19.7</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>1.13</t>
+          <t>1.45</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>0.51</t>
+          <t>0.59</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>0.85</t>
+          <t>0.56</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -1428,7 +1428,7 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>62525</t>
+          <t>542493</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -1445,22 +1445,22 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>02:055.1</t>
+          <t>02:054.7</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>16.5</t>
+          <t>17.3</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>19.3</t>
+          <t>19.6</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>1.14</t>
+          <t>1.48</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -1475,7 +1475,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>1.96</t>
+          <t>2.93</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -1485,7 +1485,7 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>58921</t>
+          <t>534381</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
